--- a/Result/checksun_type/銷售、進出口業務.xlsx
+++ b/Result/checksun_type/銷售、進出口業務.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3869358.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3871172.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3871172.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>8979574.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5956371.06</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5956371.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-403343.9373719934</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3869358</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3869358.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>37.57</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2932934.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5085370.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5085370.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>8966073.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>6139245.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>6139245.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-248911.3340451708</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2932934</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2932934.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>37.38</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3235720.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>8975058.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>8975058.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>8982585.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>6206365.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>6206365.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>80927.50406618882</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3235720</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3235720.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>37.33</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3269719.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>9730531.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>9730531.199999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8809203.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6279424.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>6279424.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>516794.2190800523</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3269719</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3269719.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>37.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6048132.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10499888.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10499888</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>8611623.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6343834.52</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>6343834.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1117361.268418428</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6048132</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6048132.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>37.59</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>38.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>9940349.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>14087975.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>14087975.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8293851.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6415232.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6415232.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1637721.329315448</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>9940349</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>9940349.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>37.79</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>38.19</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>38.43</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22381373.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>12846776.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>12846776.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>7660367.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6365776.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6365776.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1905579.547407068</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22381373</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22381373.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>37.95</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7013083.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>8990112.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>8990112.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6268708.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6009271.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>6009271.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>887210.8751305575</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7013083</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7013083.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>38.01</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>38.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>38.48</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>7116503.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7887875.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7887875.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6092590.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>6064102.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>6064102.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>1047314.88348088</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>7116503</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7116503.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>23988569.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6723359.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6723359.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5736961.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>6104545.72</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>6104545.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1227550.078142742</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>23988569</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>23988569.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>38.04</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3734356.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2499727.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2499727.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3608565.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5703808.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5703808.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-366533.5037025558</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3734356</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3734356.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>45.9</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>45.82</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>6968.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6836.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6836.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>14136.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>15532.82</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>15532.82</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1346.978568607485</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>6968</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>6968.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>46.23</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>47.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>6639.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>7324.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>7324</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>14783.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>15461.62</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>15461.62</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1187.43426458228</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>6639</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>6639.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>46.89</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>47.48</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>47.48</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14090.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>8837.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>8837.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>14830.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>15383.72</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>15383.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-881.8554636683384</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14090</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14090.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>47.69</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>47.47</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2600.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>9984.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>9984.200000000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>14662.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>15151.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>15151.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1212.140910088836</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2600</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2600.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>48.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>46.13</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>47.43</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>47.43</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3887.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>20229.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>20229</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>15048.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>15118.96</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>15118.96</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-409.6150867578017</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3887</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3887.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,21 +7937,17 @@
           <t>48.67999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AM18" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="AO18" t="inlineStr">
         <is>
           <t>46.3</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.39</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
       <c r="AP18" t="inlineStr">
         <is>
           <t>198.75</t>
@@ -8088,20 +7988,16 @@
           <t>9404.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>21436.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>21436.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>15576.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>15108.94</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>15108.94</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>613.5866282421703</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>9404</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>9404.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>48.98</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>46.48</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>14206.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>22242.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>22242.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>15118.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>15105.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>15105.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>1462.282412947767</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>14206</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>14206.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>48.58</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>46.59</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>19824.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>20823.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>20823.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>14054.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>14971.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>14971</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2107.980590636198</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>19824</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>19824.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>48.04</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>47.15</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>53824.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>19340.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>19340</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>13173.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>14799.3</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>14799.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2353.192966239807</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>53824</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>53824.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>47.06</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>46.73</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>9924.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>9868.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>9868.200000000001</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>8852.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>13770.64</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>13770.64</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1023.403388835033</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>9924</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>9924.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>46.29</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>46.81</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>46.85</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46.85</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>13434.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9716.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9716.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>9704.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>13662.1</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>13662.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1106.990917912124</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>13434</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>13434.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>156.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>164.85</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>168.36</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>168.36</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3170553681.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4138082091.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>4138082091</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4268507640.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>6060043081.46</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>6060043081.46</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-263552895.6884155</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3170553681</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3170553681.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>166.68</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>3561255788.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4508528303.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4508528303.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4128239206.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>6523283246.84</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>6523283246.84</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-197408387.5697174</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>3561255788</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>3561255788.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>168.38</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>5330763891.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>5326173063.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>5326173063.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4050371893.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>6516029437.64</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>6516029437.64</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-137726873.5940866</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>5330763891</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>5330763891.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>156.8</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>168.21</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>168.21</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3892624091.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4843786138.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4843786138.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3728171837.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>6576214335.28</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>6576214335.28</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-237138904.8933973</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3892624091</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3892624091.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>158.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>170.58</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>167.82</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>167.82</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>4735213004.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4739633072.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4739633072.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3540693680.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>6556873375.6</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>6556873375.6</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-216600438.7176485</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>4735213004</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>4735213004.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>170.95</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>170.95</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>5022784742.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4398933189.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4398933189.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3348452263.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>6518094899.78</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>6518094899.78</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-269801426.3338051</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5022784742</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5022784742.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>7649479589.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>3747950110.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>3747950110.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3187753716.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>6448828659.12</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>6448828659.12</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-366978329.6306791</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>7649479589</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>7649479589.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>166.08</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>166.08</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2918829265.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>2774570723.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>2774570723</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3016948267.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>6307955645.82</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>6307955645.82</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-774127699.0322614</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2918829265</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2918829265.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>172.2</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>165.33</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>165.33</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>3371858763.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>2612557535.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>2612557535.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3246709810.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>6279997636.12</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>6279997636.12</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-821266845.6405125</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3371858763</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3371858763.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>166.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>172.52</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>164.6</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>164.6</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>3031713588.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2341754288.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2341754288.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3717183320.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>6247764195.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>6247764195.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-907816399.6651387</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3031713588</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3031713588.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>172.38</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>163.91</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>163.91</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1767869347.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2297971337.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2297971337.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>5310238320.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>6248161668.22</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>6248161668.22</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-962592479.5337062</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1767869347</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1767869347.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>289.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>288.68</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>292.25</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>288.68</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>292.25</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>50649633.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>24804083.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>24804083</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>21975195.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>38143310.36</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>38143310.36</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>1322269.968196634</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>50649633</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>50649633.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>287.3</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>288.58</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>292.22</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>288.58</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>292.22</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>21670160.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>17205437.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>17205437.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>21410293.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>37943901.46</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>37943901.46</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1066738.421270564</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>21670160</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>21670160.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>285.5</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>288.48</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>292.23</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>292.23</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>21003510.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>18796832.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>18796832</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>25257315.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>37894928.7</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>37894928.7</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1336566.212606892</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>21003510</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>21003510.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>285.3</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>288.55</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>292.29</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>288.55</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>292.29</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>21031613.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>18342158.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>18342158</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>24358082.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>38016019.74</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>38016019.74</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1602873.192637123</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>21031613</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>21031613.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>286.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>288.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>292.46</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>292.46</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>9665499.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>17912495.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>17912495.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>23387774.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>38058834.16</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>38058834.16</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1929077.300086122</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>9665499</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>9665499.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>286.1</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>289.2</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>292.58</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>292.58</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>12656404.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>19146308.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>19146308.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>23263637.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>38375991.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>38375991.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-1108389.62143876</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>12656404</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>12656404.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>286.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>289.45</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>292.75</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>292.75</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>29627134.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>25615149.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>25615149.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>24761434.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>39336828.7</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>39336828.7</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-216847.4154625759</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>29627134</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>29627134.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>286.6</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>289.98</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>292.93</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>289.98</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>292.93</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>18730140.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>31717798.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>31717798.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>23611016.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>39509479.16</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>39509479.16</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-753763.6420872211</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>18730140</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>18730140.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>287.0</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>290.12</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>293.08</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>290.12</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>293.08</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>18883299.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>30374007.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>30374007.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>23227292.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>40163655.42</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>40163655.42</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-326331.6214764491</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>18883299</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>18883299.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>287.7</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>290.3</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>293.31</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>290.3</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>293.31</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>15834565.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>28863053.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>28863053.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>22619820.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>41997258.72</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>41997258.72</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>279530.358734522</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>15834565</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>15834565.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>288.9</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>290.98</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>293.81</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>290.98</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>293.81</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>45000608.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>27380966.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>27380966.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>23302183.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>42786182.1</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>42786182.1</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>1461714.317652535</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>45000608</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>45000608.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>10003939</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>16335914</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>11426356</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>23070340</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>23227058</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>49896013</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>34408443</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>72316895</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>17569552</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>31301475</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>17893818</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>56.36</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>54.94</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>54.94</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1557361.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1690822.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1690822</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3508385.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2296716.04</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2296716.04</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-240310.4893460944</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1557361</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1557361.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>56.12</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>54.46</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>54.94</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>54.94</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1564020.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1831265.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1831265.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>3977462.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2291569.18</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2291569.18</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-181845.1023610453</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1564020</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1564020.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>55.92</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>54.97</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>54.97</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>2083050.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1971179.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1971179.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>3937273.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2302942.54</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2302942.54</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-92542.11729808012</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2083050</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2083050.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>54.34</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>55.01</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1844728.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>2619148.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>2619148</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>3844517.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2378408.26</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2378408.26</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-17271.70587605564</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1844728</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1844728.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>54.24</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1404951.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>4457110.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>4457110.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3812701.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2401339.68</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2401339.68</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>116408.799936695</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1404951</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1404951.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>55.76000000000001</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>54.14</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>55.02</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2259579.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>5325948.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>5325948.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3791943.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2382842.64</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2382842.64</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>350342.4582428858</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2259579</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2259579.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>54.08</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>55.03</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>55.03</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2263591.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>6123659.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>6123659.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3789897.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2372429.14</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2372429.14</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>580453.8823144836</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2263591</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2263591.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>55.04</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>54.04</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>55.05</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>55.05</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5322891.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>5903366.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>5903366.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>3780568.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2348035.54</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2348035.54</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>888024.1351912492</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5322891</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5322891.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>54.36</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>55.03</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>55.03</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>11034542.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>5069886.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>5069886.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3421216.2</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2268506.2</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2268506.2</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>967912.920186941</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>11034542</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>11034542.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>53.4</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>53.81</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>54.99</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>53.81</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>54.99</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>5749141.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3168292.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>3168292.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2677041.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2090171.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2090171.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>435508.8301741099</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>5749141</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>5749141.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>53.74</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>54.99</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>54.99</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>6248132.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2257938.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2257938.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2344082.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2009452.74</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2009452.74</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>225670.6362209907</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>6248132</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>6248132.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>610.6</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>589.1</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>585.36</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>589.1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>585.36</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>136907056.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>308130393.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>308130393.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>245959950.8</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>153907736.52</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>153907736.52</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>26597568.48982471</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>136907056</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>136907056.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>609.6</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>587.65</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>584.84</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>587.65</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>584.84</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>201079064.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>312058870.6</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>312058870.6</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>246556535.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>153701668.28</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>153701668.28</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>42591194.21617693</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>201079064</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>201079064.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>607.8</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>586.35</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>584.38</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>586.35</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>584.38</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>700616207.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>304933558.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>304933558.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>235601119.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>153464011.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>153464011.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>57042544.6032452</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>700616207</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>700616207.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>604.4</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>584.4</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>583.52</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>584.4</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>583.52</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>302091104.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>228991851.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>228991851.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>177118053.4</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>142780063.72</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>142780063.72</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>22128260.38465542</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>302091104</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>302091104.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>597.8</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>582.45</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>582.52</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>582.45</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>582.52</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>199958537.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>203002399.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>203002399</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>158362712.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>139975008.1</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>139975008.1</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>14159534.66578951</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>199958537</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>199958537.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>591.2</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>581.2</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>581.62</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>581.2</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>581.62</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>156549441.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>183789508.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>183789508</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>157067733.2</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>137397945.06</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>137397945.06</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>13212718.1507743</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>156549441</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>156549441.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>587.0</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>579.95</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>580.8</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>579.95</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>580.8</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>165452503.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>181054200.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>181054200.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>153412263.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>135884355.74</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>135884355.74</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>16039214.90965346</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>165452503</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>165452503.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>583.6</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>578.8</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>580.04</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>578.8</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>580.04</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>320907671.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>166268681.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>166268681.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>147790494.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>133888063.84</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>133888063.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>18550338.81842184</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>320907671</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>320907671.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>580.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>577.65</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>579.14</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>577.65</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>579.14</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>172143843.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>125244255.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>125244255.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>128003588.2</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>128515139.64</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>128515139.64</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>4819235.730290189</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>172143843</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>172143843.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>579.8</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>576.9</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>578.48</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>576.9</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>578.48</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>103894082.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>113723026.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>113723026.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>122760008.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>126421489.12</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>126421489.12</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>970240.1854488403</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>103894082</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>103894082.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>581.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>576.6</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>578.02</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>576.6</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>578.02</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>142872904.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>130345958.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>130345958.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>135357318.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>125916800.02</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>125916800.02</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>2749498.079052299</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>142872904</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>142872904.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>61.62</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>61.27</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>61.76</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>27438023.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>28295127.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>28295127</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>48054814.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>43018314.76</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>43018314.76</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-3032782.225077435</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>27438023</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>27438023.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>61.36</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>61.79</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>61.79</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>20126832.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>27219730.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>27219730</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>48093438.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>44613807.02</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>44613807.02</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-2529493.454912305</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>20126832</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>20126832.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>61.26000000000001</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>61.14</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>61.88</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>61.88</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>42662624.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>34706537.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>34706537.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>48463333.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>45243312.38</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>45243312.38</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-936828.5527152494</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>42662624</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>42662624.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>61.4</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>61.97</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>61.97</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>30210284.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>42004980.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>42004980.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>47419499.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>44953330.72</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>44953330.72</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-1042683.958408192</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>30210284</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>30210284.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>61.92</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>62.09</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>62.09</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>21037872.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>68408887.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>68408887.40000001</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>46519228.7</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>45062406.52</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>45062406.52</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>177512.0319736078</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>21037872</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>21037872.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>61.85999999999999</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>61.19</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>22061038.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>67814502.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>67814502.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>49102358.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>45160380.1</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>45160380.1</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>2897067.874234259</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>22061038</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>22061038.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>61.85999999999999</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>62.3</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>62.3</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>57560870.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>68967146.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>68967146.40000001</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>51145979.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>45838398.06</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>45838398.06</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>6569056.010526821</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>57560870</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>57560870.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>61.15</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>62.37</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>62.37</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>79154837.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>62220128.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>62220128.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>49455209.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>45194064.56</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>45194064.56</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>7776590.7762831</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>79154837</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>79154837.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>61.34</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>61.06</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>62.4</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>162229820.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>52834018.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>52834018.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>45005338.3</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>44159152.5</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>44159152.5</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>6910265.735353388</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>162229820</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>162229820.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>60.96</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>60.92</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>62.42</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>62.42</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>18065946.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>24629570.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>24629570</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>33040029.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>41666978.42</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>41666978.42</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-3475027.706523113</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>18065946</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>18065946.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>61.14</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>62.5</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>27824259.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>30390214.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>30390214.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>34185793.5</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>42136243.64</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>42136243.64</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-2740923.705399424</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>27824259</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>27824259.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>60.36</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>58.86</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>60.54</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>60.54</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>77580224.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>79284453.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>79284453.40000001</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>84912840.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>72269039.02</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>72269039.02</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>2807953.910534963</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>77580224</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>77580224.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>59.67999999999999</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>58.78</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>60.5</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>68679719.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>72148960.4</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>72148960.40000001</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>90110205.8</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>72193962.72</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>72193962.72</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>3240003.762390554</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>68679719</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>68679719.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>59.14000000000001</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>60.48</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>88690818.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>75126830.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>75126830</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>87268579.5</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>72346830.68</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>72346830.68000001</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>4695128.952098861</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>88690818</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>88690818.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>58.67999999999999</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>58.71</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>60.47</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>60.47</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>115567139.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>74144824.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>74144824.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>81784425.9</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>72084632.36</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>72084632.36</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>4462149.724821508</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>115567139</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>115567139.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>58.78000000000001</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>58.79</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>45904367.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>75212898.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>75212898</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>72514217.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>73305435.6</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>73305435.59999999</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>1090353.945681661</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>45904367</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>45904367.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>59.06</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>58.94</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>60.48</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>41902759.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>90541228.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>90541228.40000001</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>71510331.3</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>73138507.26</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>73138507.26000001</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>3698430.048850372</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>41902759</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>41902759.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>59.5</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>59.07</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>83569067.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>108071451.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>108071451.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>73551967.7</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>73167175.2</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>73167175.2</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>7720909.980203897</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>83569067</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>83569067.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>59.5</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>59.21</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>83780792.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>99410329.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>99410329</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>72742387.5</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>73230595.74</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>73230595.73999999</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>8727315.811415926</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>83780792</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>83780792.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>59.38</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>59.25</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>60.49</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>60.49</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>120907505.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>89424027.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>89424027</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>68150476.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>72428984.18</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>72428984.18000001</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>9830663.755596831</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>120907505</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>120907505.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>59.16</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>60.46</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>60.46</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>122546019.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>69815537.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>69815537.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>58939461.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>71232340.72</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>71232340.72</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>7077917.86315538</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>122546019</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>122546019.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>58.34</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>59.06</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>60.41</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>60.41</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>129553873.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>52479434.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>52479434.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>53076655.8</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>69459357.48</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>69459357.48</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>2717085.878840625</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>129553873</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>129553873.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>15398999.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>34221878.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>34221878.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>36617575.1</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>25241855.24</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>25241855.24</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>2053470.207403455</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>15398999</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>15398999.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>27.15</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>31549272.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>38918740.8</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>38918740.8</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>36738077.3</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>25462351.56</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>25462351.56</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>4244409.746218462</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>31549272</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>31549272.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>25.79</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>25.79</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>66917706.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>44512832.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>44512832.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>34620079.0</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>25398329.14</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>25398329.14</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>5492350.917874958</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>66917706</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>66917706.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>26.13</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>25.73</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>38460831.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>40957668.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>40957668.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>29797516.3</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>24401116.96</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>24401116.96</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>3289493.558888707</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>38460831</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>38460831.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>25.69</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>18782585.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>40170944.4</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>40170944.4</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>26760865.4</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>24094528.78</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>24094528.78</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>3074023.454662319</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>18782585</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>18782585.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>25.66</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>38883310.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>39013271.6</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>39013271.6</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>27803305.8</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>23943921.98</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>23943921.98</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>4764805.968100969</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>38883310</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>38883310.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>25.63</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>59519729.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>34557413.8</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>34557413.8</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>25421344.0</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>23374106.74</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>23374106.74</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>4856388.809866868</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>59519729</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>59519729.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>25.59</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>25.59</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>49141889.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>24727325.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>24727325.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>20699524.6</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>22332782.62</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>22332782.62</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>2602734.090608615</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>49141889</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>49141889.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>26.12</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>34527209.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>18637363.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>18637363.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>17271105.9</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>21698630.5</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>21698630.5</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>402183.988432236</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>34527209</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>34527209.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>25.84</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>25.5</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>12994221.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>13350786.4</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>13350786.4</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>15342192.5</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>21347314.02</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>21347314.02</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-1189964.157120883</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>12994221</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>12994221.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>25.92000000000001</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>25.48</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>16604021.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>16593340.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>16593340</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>16535240.3</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>21345209.82</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>21345209.82</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-1114856.930871021</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>16604021</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>16604021.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>12.09</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>12.75</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>875756.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>676314.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>676314.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>999130.2</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>1048454.2</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>1048454.2</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-28533.59288544348</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>875756</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>875756.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>12.01</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>12.76</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>12.76</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>232591.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>746328.4</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>746328.4</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>999519.1</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>1052499.42</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>1052499.42</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-41241.79391897016</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>232591</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>232591.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>12.1</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>12.78</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>635346.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>795945.8</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>795945.8</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>1046717.3</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>1051933.08</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>1051933.08</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>10987.09010166931</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>635346</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>635346.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>12.25</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>12.8</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>871710.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>1165824.2</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>1165824.2</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>999445.3</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>1047142.14</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>1047142.14</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>42055.06405609474</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>871710</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>871710.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>12.37</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>12.26</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>12.82</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>12.82</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>766168.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>1353716.0</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>1353716</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>925971.4</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>1051975.58</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>1051975.58</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>59611.20313184173</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>766168</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>766168.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>12.37</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>12.84</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>1225827.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>1321946.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>1321946.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>884885.8</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>1095711.4</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>1095711.4</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>93870.50169962889</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>1225827</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>1225827.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>12.43</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>480678.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>1252709.8</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>1252709.8</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>783889.7</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>1181635.08</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>1181635.08</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>90210.66030719539</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>480678</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>480678.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>12.32</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>2484738.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>1297488.8</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>1297488.8</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>796517.5</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>1206824.18</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>1206824.18</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>161597.8990213191</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>2484738</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>2484738.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>12.19</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>1811169.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>833066.4</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>833066.4</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>753734.6</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>1196733.68</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>1196733.68</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>43087.60079073429</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>1811169</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>1811169.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>12.13</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>607319.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>498226.8</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>498226.8</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>632945.1</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>1185112.74</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>1185112.74</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-55583.56099548459</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>607319</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>607319.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>12.16</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>879645.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>447825.4</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>447825.4</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>600325.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>1177667.04</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>1177667.04</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-65573.30779738701</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>879645</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>879645.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>11.8</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>12.14</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>12.15</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>18005548.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>19177580.6</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>19177580.6</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>29580981.1</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>22421239.98</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>22421239.98</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-1785117.168213371</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>18005548</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>18005548.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,21 +53517,17 @@
           <t>11.71</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
+      <c r="AM124" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AO124" t="inlineStr">
         <is>
           <t>12.17</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>12.17</t>
-        </is>
-      </c>
       <c r="AP124" t="inlineStr">
         <is>
           <t>-186.05</t>
@@ -54304,20 +53568,16 @@
           <t>7727015.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>21268995.2</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>21268995.2</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>30374102.1</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>22678426.12</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>22678426.12</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-1555011.203350872</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>7727015</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>7727015.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,21 +53947,17 @@
           <t>11.74</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
+      <c r="AM125" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AO125" t="inlineStr">
         <is>
           <t>12.18</t>
         </is>
       </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>12.18</t>
-        </is>
-      </c>
       <c r="AP125" t="inlineStr">
         <is>
           <t>-383.32</t>
@@ -54740,20 +53998,16 @@
           <t>18977250.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>27449635.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>27449635.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>30912071.6</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>23124120.4</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>23124120.4</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-69480.88914190978</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>18977250</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>18977250.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>20356352.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>32034183.2</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>32034183.2</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>30173949.8</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>23085176.4</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>23085176.4</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>849804.4129116759</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>20356352</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>20356352.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>12.18</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>30821738.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>41658482.4</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>41658482.4</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>29511896.2</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>23187205.66</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>23187205.66</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>1984958.043955665</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>30821738</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>30821738.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>12.35</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>28462621.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>39984381.6</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>39984381.6</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>27721210.7</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>22822287.78</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>22822287.78</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>2414423.37244866</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>28462621</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>28462621.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>12.52</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>38630216.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>39479209.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>39479209</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>26345598.1</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>22740925.0</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>22740925</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>3194478.399851203</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>38630216</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>38630216.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>12.54</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>12.23</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>41899989.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>34374507.8</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>34374507.8</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>25719252.4</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>22198404.0</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>22198404</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>3105369.03186015</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>41899989</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>41899989.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>12.4</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>12.44</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>12.22</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>12.22</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>68477848.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>28313716.4</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>28313716.4</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>23284004.4</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>21757255.78</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>21757255.78</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>2516831.076449357</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>68477848</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>68477848.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>12.38</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>12.2</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>22451234.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>17365310.0</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>17365310</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>18118301.0</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>20655784.36</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>20655784.36</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-1261452.005439252</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>22451234</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>22451234.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>25936758.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>15458039.8</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>15458039.8</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>18385630.8</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>20507029.94</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>20507029.94</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-1682524.479371578</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>25936758</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>25936758.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57633,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57817,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>17.64</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>17.64</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57868,16 @@
           <t>6791803.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>10058420.4</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>10058420.4</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>20353292.4</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>15094194.92</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>15094194.92</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57894,10 @@
           <t>-1996695.871977523</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>6791803</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>6791803.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58063,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58247,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>17.63</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58298,16 @@
           <t>5688835.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>12748490.6</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>12748490.6</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>23731866.1</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>15360881.76</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>15360881.76</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58324,10 @@
           <t>-1408807.419375379</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>5688835</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>5688835.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58493,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58677,11 @@
           <t>17.99</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>17.7</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58728,16 @@
           <t>16688578.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>15079634.6</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>15079634.6</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>25532824.5</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>15494092.0</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>15494092</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58754,10 @@
           <t>-400477.0792517662</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>16688578</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>16688578.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59107,11 @@
           <t>18.07</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>17.66</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59158,16 @@
           <t>11811096.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>17474774.8</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>17474774.8</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>25895143.3</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>15509598.64</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>15509598.64</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59184,10 @@
           <t>-124246.3048161827</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>11811096</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>11811096.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59353,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59537,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>17.63</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59588,16 @@
           <t>9311790.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>28417473.0</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>28417473</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>26672932.2</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>15411366.58</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>15411366.58</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59614,10 @@
           <t>797393.8124066554</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>9311790</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>9311790.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59783,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59967,11 @@
           <t>18.33</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60018,16 @@
           <t>20242154.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>30648164.4</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>30648164.4</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>26970051.1</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>15411161.88</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>15411161.88</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60044,10 @@
           <t>2353326.986567616</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>20242154</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>20242154.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60213,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60397,11 @@
           <t>18.4</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>17.58</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60448,16 @@
           <t>17344555.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>34715241.6</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>34715241.6</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>26279480.7</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>15172436.36</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>15172436.36</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60474,10 @@
           <t>3320930.842991576</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>17344555</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>17344555.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60643,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60827,11 @@
           <t>18.37</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>17.62</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>17.62</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60878,16 @@
           <t>28664279.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>35986014.4</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>35986014.4</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>26734953.5</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>14965321.98</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>14965321.98</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60904,10 @@
           <t>4895074.429204676</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>28664279</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>28664279.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61073,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61257,11 @@
           <t>18.17</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>17.48</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>17.6</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61308,16 @@
           <t>66524587.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>34315511.8</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>34315511.8</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>25013118.4</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>14532416.86</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>14532416.86</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61334,10 @@
           <t>5756199.32275179</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>66524587</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>66524587.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61687,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>17.42</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>17.57</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>17.57</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61738,16 @@
           <t>20465247.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>24928391.4</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>24928391.4</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>19851734.8</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>13542466.52</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>13542466.52</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61764,10 @@
           <t>2724337.623435102</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>20465247</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>20465247.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61933,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62117,11 @@
           <t>17.72</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>17.38</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>17.56</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>17.56</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62168,16 @@
           <t>40577540.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>23291937.8</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>23291937.8</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>18777885.8</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>13347392.76</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>13347392.76</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62194,10 @@
           <t>3230738.137860011</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>40577540</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>40577540.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
